--- a/output/tests/SearchSong/SongCard.xlsx
+++ b/output/tests/SearchSong/SongCard.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Nome</t>
   </si>
@@ -39,142 +39,175 @@
     <t>SongCard</t>
   </si>
   <si>
+    <t>mutation_a_attr_val_mod_mut_gamma</t>
+  </si>
+  <si>
+    <t>HookXPathTest</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application did not recompile. Marking test as not applicable.</t>
+  </si>
+  <si>
+    <t>SeleniumXPathTest</t>
+  </si>
+  <si>
+    <t>RobulaXPathTest</t>
+  </si>
+  <si>
+    <t>KatalonXPathTest</t>
+  </si>
+  <si>
+    <t>RelativeXPathTest</t>
+  </si>
+  <si>
+    <t>RobulaPlusXPathTest</t>
+  </si>
+  <si>
+    <t>AbsoluteXPathTest</t>
+  </si>
+  <si>
+    <t>mutation_k_tag_ins_mut_alpha</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.cssSelector .ng-dirty (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element Unable to locate element {method xpath selector(.//*[normalize-space(text()) and normalize-space(.)='Michael Jackson'])[10]/followinga[1]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid selector Unable to locate an element with the xpath expression //input[@placeholder='Artists  songs  albums  or playlists']) because of the following error SyntaxError Failed to execute 'evaluate' on 'Document' The string '//input[@placeholder='Artists  songs  albums  or playlists'])' is not a valid XPath expression.</t>
+  </si>
+  <si>
+    <t>mutation_j_tag_type_mod_mut_beta</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.xpath //as-album-track[@ng-reflect-index='1']/*/as-track-main-info (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.xpath //*[@ng-reflect-index='1']/*/as-track-main-info (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.xpath /html[1]/body[1]/angular-spotify-root[1]/as-layout[1]/as-main-view[1]/div[2]/as-search[1]/div[1]/div[2]/div[1]/as-album-track[1]/as-media-table-row[1]/as-track-main-info[1] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>mutation_a_attr_val_mod_mut_alpha</t>
+  </si>
+  <si>
+    <t>mutation_h_tag_mov_temp_mut_gamma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.xpath //*[@x-test-tpl-html-1]//*[@x-test-hook-angular-spotify-root-29]//*[@x-test-tpl-as-main-view-3]//*[@x-test-tpl-div-2]//*[@x-test-tpl-div-1]//*[@x-test-hook-as-album-track-13][1]//*[@x-test-tpl-as-media-table-row-1]//*[@x-test-hook-as-track-main-info-4] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for visibility of element located by By.xpath (.//*[normalize-space(text()) and normalize-space(.)='Title'])[1]/followingas-track-main-info[1] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>mutation_b_attr_rem_mut_delta</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for element to be clickable By.xpath //a[normalize-space()='Search'] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for element to be clickable By.xpath //*[@ng-reflect-router-link='/search'] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected condition failed waiting for element to be clickable By.xpath /html[1]/body[1]/angular-spotify-root[1]/as-layout[1]/as-nav-bar[1]/ul[1]/li[2]/a[1] (tried for 10 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>mutation_j_tag_type_mod_mut_gamma</t>
+  </si>
+  <si>
+    <t>mutation_i_tag_rem_mut_alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid selector Unable to locate an element with the xpath expression //input[@placeholder='Artists  songs  albums  or playlists']) because of the following error</t>
+  </si>
+  <si>
+    <t>mutation_i_tag_rem_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_a_attr_val_mod_mut_beta</t>
+  </si>
+  <si>
+    <t>mutation_b_attr_rem_mut_gamma</t>
+  </si>
+  <si>
+    <t>mutation_k_tag_ins_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_b_attr_rem_mut_beta</t>
+  </si>
+  <si>
+    <t>mutation_h_tag_mov_temp_mut_alpha</t>
+  </si>
+  <si>
+    <t>mutation_j_tag_type_mod_mut_alpha</t>
+  </si>
+  <si>
+    <t>mutation_a_attr_val_mod_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_k_tag_ins_mut_beta</t>
+  </si>
+  <si>
     <t>mutation_g_tag_mov_html_mut_gamma</t>
   </si>
   <si>
-    <t>SeleniumXPathTest</t>
-  </si>
-  <si>
-    <t>gamma</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected:&lt;[Michael Jackson]&gt; but was:&lt;[Songs]&gt;</t>
-  </si>
-  <si>
-    <t>HookTest</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>RobulaXPathTest</t>
-  </si>
-  <si>
-    <t>KatalonXPathTest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected:&lt;[Michael Jackson]&gt; but was:&lt;[Billy Joel]&gt;</t>
-  </si>
-  <si>
-    <t>RelativeXPathTest</t>
-  </si>
-  <si>
-    <t>AbsoluteXPathTest</t>
+    <t>mutation_g_tag_mov_html_mut_alpha</t>
+  </si>
+  <si>
+    <t>mutation_b_attr_rem_mut_alpha</t>
+  </si>
+  <si>
+    <t>mutation_g_tag_mov_html_mut_beta</t>
+  </si>
+  <si>
+    <t>mutation_i_tag_rem_mut_beta</t>
   </si>
   <si>
     <t>mutation_h_tag_mov_temp_mut_delta</t>
   </si>
   <si>
-    <t>delta</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application did not recompile. Marking test as not applicable.</t>
-  </si>
-  <si>
-    <t>mutation_h_tag_mov_temp_mut_gamma</t>
-  </si>
-  <si>
-    <t>mutation_a_attr_val_mod_mut_gamma</t>
-  </si>
-  <si>
-    <t>mutation_j_tag_type_mod_mut_beta</t>
-  </si>
-  <si>
-    <t>beta</t>
-  </si>
-  <si>
-    <t>mutation_j_tag_type_mod_mut_gamma</t>
-  </si>
-  <si>
-    <t>mutation_i_tag_rem_mut_alpha</t>
-  </si>
-  <si>
-    <t>alpha</t>
-  </si>
-  <si>
-    <t>mutation_h_tag_mov_temp_mut_alpha</t>
-  </si>
-  <si>
-    <t>mutation_b_attr_rem_mut_gamma</t>
-  </si>
-  <si>
-    <t>mutation_g_tag_mov_html_mut_alpha</t>
+    <t>mutation_g_tag_mov_html_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_j_tag_type_mod_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_f_tag_mov_container_mut_delta</t>
+  </si>
+  <si>
+    <t>mutation_k_tag_ins_mut_gamma</t>
   </si>
   <si>
     <t>mutation_i_tag_rem_mut_gamma</t>
   </si>
   <si>
-    <t>mutation_i_tag_rem_mut_beta</t>
-  </si>
-  <si>
-    <t>mutation_g_tag_mov_html_mut_beta</t>
-  </si>
-  <si>
-    <t>mutation_j_tag_type_mod_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_b_attr_rem_mut_alpha</t>
-  </si>
-  <si>
     <t>mutation_h_tag_mov_temp_mut_beta</t>
-  </si>
-  <si>
-    <t>mutation_b_attr_rem_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_a_attr_val_mod_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_a_attr_val_mod_mut_alpha</t>
-  </si>
-  <si>
-    <t>mutation_i_tag_rem_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_k_tag_ins_mut_beta</t>
-  </si>
-  <si>
-    <t>mutation_k_tag_ins_mut_alpha</t>
-  </si>
-  <si>
-    <t>mutation_f_tag_mov_container_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_b_attr_rem_mut_beta</t>
-  </si>
-  <si>
-    <t>mutation_g_tag_mov_html_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_j_tag_type_mod_mut_alpha</t>
-  </si>
-  <si>
-    <t>mutation_k_tag_ins_mut_gamma</t>
-  </si>
-  <si>
-    <t>mutation_k_tag_ins_mut_delta</t>
-  </si>
-  <si>
-    <t>mutation_a_attr_val_mod_mut_beta</t>
   </si>
 </sst>
 </file>
@@ -293,8 +326,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table1" ref="$A$1:$F$175">
-  <autoFilter ref="$A$1:$F$175"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table1" ref="$A$1:$F$204">
+  <autoFilter ref="$A$1:$F$204"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nome"/>
     <tableColumn id="2" name="Identificativo"/>
@@ -789,12 +822,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="9.00390625"/>
+    <col bestFit="1" min="1" max="1" width="9.00390625"/>
     <col bestFit="1" min="2" max="2" width="37.8515625"/>
-    <col bestFit="1" min="3" max="3" width="17.28125"/>
+    <col bestFit="1" min="3" max="3" width="19.00390625"/>
     <col bestFit="1" min="4" max="4" width="7.140625"/>
     <col bestFit="1" min="5" max="5" width="15.57421875"/>
-    <col bestFit="1" min="6" max="6" width="52.8515625"/>
+    <col bestFit="1" min="6" max="6" width="255.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -851,10 +884,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -865,16 +898,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -885,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>9</v>
@@ -894,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -905,16 +938,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -925,16 +958,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -942,19 +975,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -962,19 +995,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -982,13 +1015,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>22</v>
@@ -1002,19 +1035,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -1022,19 +1055,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="14.25">
@@ -1042,19 +1075,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E13" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="14.25">
@@ -1062,19 +1095,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="14.25">
@@ -1082,19 +1115,19 @@
         <v>6</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="14.25">
@@ -1102,19 +1135,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="14.25">
@@ -1122,13 +1155,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>22</v>
@@ -1142,19 +1175,19 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="14.25">
@@ -1162,19 +1195,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20" ht="14.25">
@@ -1182,19 +1215,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21" ht="14.25">
@@ -1202,19 +1235,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="14.25">
@@ -1222,19 +1255,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="14.25">
@@ -1242,19 +1275,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="14.25">
@@ -1262,19 +1295,19 @@
         <v>6</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="14.25">
@@ -1282,19 +1315,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="14.25">
@@ -1302,13 +1335,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>10</v>
@@ -1322,19 +1355,19 @@
         <v>6</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" ht="14.25">
@@ -1342,19 +1375,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="14.25">
@@ -1362,19 +1395,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" ht="14.25">
@@ -1382,19 +1415,19 @@
         <v>6</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="14.25">
@@ -1402,19 +1435,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="14.25">
@@ -1422,19 +1455,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" ht="14.25">
@@ -1442,19 +1475,19 @@
         <v>6</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" ht="14.25">
@@ -1462,7 +1495,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>15</v>
@@ -1471,10 +1504,10 @@
         <v>9</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" ht="14.25">
@@ -1482,7 +1515,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>16</v>
@@ -1491,10 +1524,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" ht="14.25">
@@ -1502,19 +1535,19 @@
         <v>6</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" ht="14.25">
@@ -1522,19 +1555,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" ht="14.25">
@@ -1542,19 +1575,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" ht="14.25">
@@ -1562,19 +1595,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" ht="14.25">
@@ -1582,19 +1615,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" ht="14.25">
@@ -1602,19 +1635,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" ht="14.25">
@@ -1622,19 +1655,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" ht="14.25">
@@ -1642,19 +1675,19 @@
         <v>6</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" ht="14.25">
@@ -1662,19 +1695,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" ht="14.25">
@@ -1682,13 +1715,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>22</v>
@@ -1702,19 +1735,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" ht="14.25">
@@ -1722,19 +1755,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" ht="14.25">
@@ -1742,19 +1775,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" ht="14.25">
@@ -1762,19 +1795,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" ht="14.25">
@@ -1782,19 +1815,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" ht="14.25">
@@ -1802,19 +1835,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" ht="14.25">
@@ -1822,19 +1855,19 @@
         <v>6</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" ht="14.25">
@@ -1842,19 +1875,19 @@
         <v>6</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" ht="14.25">
@@ -1862,19 +1895,19 @@
         <v>6</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -1882,19 +1915,19 @@
         <v>6</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E55" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -1902,19 +1935,19 @@
         <v>6</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" ht="14.25">
@@ -1922,19 +1955,19 @@
         <v>6</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" ht="14.25">
@@ -1942,19 +1975,19 @@
         <v>6</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="59" ht="14.25">
@@ -1962,13 +1995,13 @@
         <v>6</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>22</v>
@@ -1982,19 +2015,19 @@
         <v>6</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" ht="14.25">
@@ -2002,19 +2035,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" ht="14.25">
@@ -2022,19 +2055,19 @@
         <v>6</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" ht="14.25">
@@ -2042,19 +2075,19 @@
         <v>6</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" ht="14.25">
@@ -2062,19 +2095,19 @@
         <v>6</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" ht="14.25">
@@ -2082,19 +2115,19 @@
         <v>6</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" ht="14.25">
@@ -2102,19 +2135,19 @@
         <v>6</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" ht="14.25">
@@ -2122,19 +2155,19 @@
         <v>6</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" ht="14.25">
@@ -2142,19 +2175,19 @@
         <v>6</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" ht="14.25">
@@ -2162,19 +2195,19 @@
         <v>6</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" ht="14.25">
@@ -2182,19 +2215,19 @@
         <v>6</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" ht="14.25">
@@ -2202,19 +2235,19 @@
         <v>6</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" ht="14.25">
@@ -2222,19 +2255,19 @@
         <v>6</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" ht="14.25">
@@ -2242,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>22</v>
@@ -2262,19 +2295,19 @@
         <v>6</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" ht="14.25">
@@ -2282,19 +2315,19 @@
         <v>6</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" ht="14.25">
@@ -2302,19 +2335,19 @@
         <v>6</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" ht="14.25">
@@ -2322,19 +2355,19 @@
         <v>6</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" ht="14.25">
@@ -2342,19 +2375,19 @@
         <v>6</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" ht="14.25">
@@ -2362,19 +2395,19 @@
         <v>6</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" ht="14.25">
@@ -2382,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>22</v>
@@ -2402,19 +2435,19 @@
         <v>6</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="82" ht="14.25">
@@ -2422,19 +2455,19 @@
         <v>6</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" ht="14.25">
@@ -2442,19 +2475,19 @@
         <v>6</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" ht="14.25">
@@ -2462,19 +2495,19 @@
         <v>6</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="85" ht="14.25">
@@ -2482,19 +2515,19 @@
         <v>6</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="86" ht="14.25">
@@ -2502,13 +2535,13 @@
         <v>6</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>10</v>
@@ -2522,19 +2555,19 @@
         <v>6</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" ht="14.25">
@@ -2542,19 +2575,19 @@
         <v>6</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" ht="14.25">
@@ -2562,19 +2595,19 @@
         <v>6</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" ht="14.25">
@@ -2582,19 +2615,19 @@
         <v>6</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" ht="14.25">
@@ -2602,19 +2635,19 @@
         <v>6</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" ht="14.25">
@@ -2622,10 +2655,10 @@
         <v>6</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>27</v>
@@ -2642,19 +2675,19 @@
         <v>6</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" ht="14.25">
@@ -2662,19 +2695,19 @@
         <v>6</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" ht="14.25">
@@ -2682,19 +2715,19 @@
         <v>6</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" ht="14.25">
@@ -2702,19 +2735,19 @@
         <v>6</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" ht="14.25">
@@ -2722,19 +2755,19 @@
         <v>6</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="E97" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" ht="14.25">
@@ -2742,13 +2775,13 @@
         <v>6</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>10</v>
@@ -2762,19 +2795,19 @@
         <v>6</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" ht="14.25">
@@ -2782,19 +2815,19 @@
         <v>6</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" ht="14.25">
@@ -2802,19 +2835,19 @@
         <v>6</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" ht="14.25">
@@ -2822,19 +2855,19 @@
         <v>6</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" ht="14.25">
@@ -2842,19 +2875,19 @@
         <v>6</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E103" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" ht="14.25">
@@ -2862,19 +2895,19 @@
         <v>6</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" ht="14.25">
@@ -2882,19 +2915,19 @@
         <v>6</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" ht="14.25">
@@ -2902,19 +2935,19 @@
         <v>6</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" ht="14.25">
@@ -2922,19 +2955,19 @@
         <v>6</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" ht="14.25">
@@ -2942,19 +2975,19 @@
         <v>6</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" ht="14.25">
@@ -2962,19 +2995,19 @@
         <v>6</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" ht="14.25">
@@ -2982,19 +3015,19 @@
         <v>6</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" ht="14.25">
@@ -3002,19 +3035,19 @@
         <v>6</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" ht="14.25">
@@ -3022,19 +3055,19 @@
         <v>6</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" ht="14.25">
@@ -3042,19 +3075,19 @@
         <v>6</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" ht="14.25">
@@ -3062,19 +3095,19 @@
         <v>6</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115" ht="14.25">
@@ -3082,13 +3115,13 @@
         <v>6</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>22</v>
@@ -3102,19 +3135,19 @@
         <v>6</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" ht="14.25">
@@ -3122,19 +3155,19 @@
         <v>6</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" ht="14.25">
@@ -3142,19 +3175,19 @@
         <v>6</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" ht="14.25">
@@ -3162,19 +3195,19 @@
         <v>6</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" ht="14.25">
@@ -3182,19 +3215,19 @@
         <v>6</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" ht="14.25">
@@ -3202,19 +3235,19 @@
         <v>6</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" ht="14.25">
@@ -3222,13 +3255,13 @@
         <v>6</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>10</v>
@@ -3242,19 +3275,19 @@
         <v>6</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" ht="14.25">
@@ -3262,19 +3295,19 @@
         <v>6</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" ht="14.25">
@@ -3282,19 +3315,19 @@
         <v>6</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" ht="14.25">
@@ -3302,19 +3335,19 @@
         <v>6</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" ht="14.25">
@@ -3322,19 +3355,19 @@
         <v>6</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" ht="14.25">
@@ -3342,13 +3375,13 @@
         <v>6</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>10</v>
@@ -3362,19 +3395,19 @@
         <v>6</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" ht="14.25">
@@ -3382,19 +3415,19 @@
         <v>6</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" ht="14.25">
@@ -3402,19 +3435,19 @@
         <v>6</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" ht="14.25">
@@ -3422,19 +3455,19 @@
         <v>6</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" ht="14.25">
@@ -3442,19 +3475,19 @@
         <v>6</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C133" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D133" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E133" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" ht="14.25">
@@ -3462,13 +3495,13 @@
         <v>6</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>10</v>
@@ -3482,19 +3515,19 @@
         <v>6</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136" ht="14.25">
@@ -3502,19 +3535,19 @@
         <v>6</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" ht="14.25">
@@ -3522,19 +3555,19 @@
         <v>6</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" ht="14.25">
@@ -3542,19 +3575,19 @@
         <v>6</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" ht="14.25">
@@ -3562,19 +3595,19 @@
         <v>6</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C139" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D139" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E139" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" ht="14.25">
@@ -3582,19 +3615,19 @@
         <v>6</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" ht="14.25">
@@ -3602,19 +3635,19 @@
         <v>6</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" ht="14.25">
@@ -3622,19 +3655,19 @@
         <v>6</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" ht="14.25">
@@ -3642,19 +3675,19 @@
         <v>6</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" ht="14.25">
@@ -3662,19 +3695,19 @@
         <v>6</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" ht="14.25">
@@ -3682,19 +3715,19 @@
         <v>6</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" ht="14.25">
@@ -3702,13 +3735,13 @@
         <v>6</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>10</v>
@@ -3722,19 +3755,19 @@
         <v>6</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" ht="14.25">
@@ -3742,19 +3775,19 @@
         <v>6</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" ht="14.25">
@@ -3762,19 +3795,19 @@
         <v>6</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" ht="14.25">
@@ -3782,19 +3815,19 @@
         <v>6</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" ht="14.25">
@@ -3802,19 +3835,19 @@
         <v>6</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" ht="14.25">
@@ -3822,19 +3855,19 @@
         <v>6</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" ht="14.25">
@@ -3842,19 +3875,19 @@
         <v>6</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" ht="14.25">
@@ -3862,19 +3895,19 @@
         <v>6</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" ht="14.25">
@@ -3882,19 +3915,19 @@
         <v>6</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" ht="14.25">
@@ -3902,19 +3935,19 @@
         <v>6</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" ht="14.25">
@@ -3922,13 +3955,13 @@
         <v>6</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>22</v>
@@ -3942,19 +3975,19 @@
         <v>6</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" ht="14.25">
@@ -3962,19 +3995,19 @@
         <v>6</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" ht="14.25">
@@ -3982,19 +4015,19 @@
         <v>6</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" ht="14.25">
@@ -4002,19 +4035,19 @@
         <v>6</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162" ht="14.25">
@@ -4022,19 +4055,19 @@
         <v>6</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163" ht="14.25">
@@ -4042,19 +4075,19 @@
         <v>6</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="164" ht="14.25">
@@ -4062,19 +4095,19 @@
         <v>6</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" ht="14.25">
@@ -4082,19 +4115,19 @@
         <v>6</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166" ht="14.25">
@@ -4102,19 +4135,19 @@
         <v>6</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" ht="14.25">
@@ -4122,19 +4155,19 @@
         <v>6</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" ht="14.25">
@@ -4142,19 +4175,19 @@
         <v>6</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" ht="14.25">
@@ -4162,19 +4195,19 @@
         <v>6</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" ht="14.25">
@@ -4182,19 +4215,19 @@
         <v>6</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" ht="14.25">
@@ -4202,19 +4235,19 @@
         <v>6</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" ht="14.25">
@@ -4222,19 +4255,19 @@
         <v>6</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" ht="14.25">
@@ -4242,19 +4275,19 @@
         <v>6</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" ht="14.25">
@@ -4262,19 +4295,19 @@
         <v>6</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" ht="14.25">
@@ -4282,28 +4315,608 @@
         <v>6</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D175" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" ht="14.25">
+      <c r="A176" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" ht="14.25">
+      <c r="A177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" ht="14.25">
+      <c r="A178" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" ht="14.25">
+      <c r="A179" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="180" ht="14.25">
+      <c r="A180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="181" ht="14.25">
+      <c r="A181" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" ht="14.25">
+      <c r="A182" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" ht="14.25">
+      <c r="A183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184" ht="14.25">
+      <c r="A184" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" ht="14.25">
+      <c r="A185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" ht="14.25">
+      <c r="A186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="187" ht="14.25">
+      <c r="A187" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="188" ht="14.25">
+      <c r="A188" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" ht="14.25">
+      <c r="A189" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="190" ht="14.25">
+      <c r="A190" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" ht="14.25">
+      <c r="A191" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192" ht="14.25">
+      <c r="A192" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" ht="14.25">
+      <c r="A193" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25">
+      <c r="A194" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="195" ht="14.25">
+      <c r="A195" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25">
+      <c r="A196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25">
+      <c r="A197" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25">
+      <c r="A198" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E175" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="176" ht="14.25">
-      <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
+      <c r="E198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" ht="14.25">
+      <c r="A199" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25">
+      <c r="A200" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25">
+      <c r="A201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25">
+      <c r="A202" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" ht="14.25">
+      <c r="A203" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25">
+      <c r="A204" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" ht="14.25">
+      <c r="A205" s="4"/>
+      <c r="B205" s="4"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -4313,62 +4926,5 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" text="FAILED" id="{007400A0-0036-4E07-AFA2-008D00210058}">
-            <xm:f>NOT(ISERROR(SEARCH("FAILED",E2)))</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>E2:E175</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" text="PASSED" id="{009D0066-00D0-4510-B4EF-00E900C6009A}">
-            <xm:f>NOT(ISERROR(SEARCH("PASSED",E2)))</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>E2:E175</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" text="NOT" id="{00740021-00B5-46DE-8D5A-000B008200C9}">
-            <xm:f>NOT(ISERROR(SEARCH("NOT",E2)))</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C5700"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>E2:E175</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>